--- a/Översikt SMEDJEBACKEN.xlsx
+++ b/Översikt SMEDJEBACKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45629</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45869</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45517</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>44859</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>45967</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>46174</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>44823</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45001</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45609</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45862</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45049</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45453</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45644</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45862</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45945</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45960</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45251</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45391</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>45723</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45553</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>46155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>44615</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44701</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>44829</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45607</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45763</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>45454</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>46163</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>44482</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>45063</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>45063</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>45720</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>46085</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>45064</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45540</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45225</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>45225</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>44826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>45698</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>46140</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>45726</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44727</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>45975</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>46162</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45999</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45433</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45723</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44476</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45565</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45226</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>45441</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>45109</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>46199</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>46199</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>46129</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>45579</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>45401</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45517</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>45723</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>45527</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>45786</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>45517</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45786</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45792</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46282</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>46282</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>45642</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45251</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>44585</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>46029</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>46282</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44882</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44613</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44787</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44571</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>44735</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44809</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>44462</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>44691</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44496</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>44641</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>44713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44706</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>44496</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>44832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>44475</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44461</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>44826</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>44537</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>44509</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44563</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44563</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44791</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>44467</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>44496</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>44656</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>44509</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>44525</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>44734</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44608</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>44790</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44799</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44496</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>44496</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>44804</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>44778</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>44784</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>44630</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>44803</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>44714</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44496</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44861</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44811</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>44876</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>44545</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>44469</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>44574</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44770</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>44787</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44787</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>44531</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>44581</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>44791</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>44831</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>45429</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45469</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45153</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>44855</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>44718</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45527</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>44880</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>45107</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>45205</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44515</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>44683</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>45219</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45462</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>44700</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45019</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44876</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>44776</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>44496</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>44914</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45310</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>45172</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45501</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>44860</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>44568</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>45615</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>44809</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44895</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45420</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44914</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44914</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45670</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>44859</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45424</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44987</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>44482</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44482</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44909</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45642</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>44477</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45446</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45264</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45644</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44630</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45698</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45558</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45006</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>45429</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>45154</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>45758</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>45250</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45208</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45229</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>45371</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44617</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>45582</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45378</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>44890</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44473</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45319</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>44734</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45407</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45463</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>44683</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>44683</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>44494</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45063</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45700</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44937</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>45175</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45063</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45467</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>44477</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>45884</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45428</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>45124</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45162</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45818</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45891</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45891</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>45579</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45469</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45891</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45891</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>45082</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45891</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45454</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>46136</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45887</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>45751</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>45903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45106</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>45907</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>46141</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>46141</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>45429</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45603</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>45747</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45401</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45589</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>45919</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>45077</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>45471</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>45922</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45198</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45925</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>46036</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45125</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>44659</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45412</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>44883</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45121</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45246</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>45931</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45935</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45936</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45936</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45936</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>46146</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45936</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>46146</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44895</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45938</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45478</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45596</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>46149</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45945</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45945</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>46149</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45945</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45947</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>44475</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45947</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45947</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45946</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45947</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45947</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45947</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>45947</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45947</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>44897</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45950</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45950</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>45950</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45950</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>44896</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45462</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>45462</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45953</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45952</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45952</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44778</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45957</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45625</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45919</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45954</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>46150</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45958</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>46150</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>46150</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>44666</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45960</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45887</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>45887</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45964</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>45964</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45964</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45743</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>46155</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45106</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>45428</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44845</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45971</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45973</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45973</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44686</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44503</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>45975</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45208</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44966</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>45226</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45980</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45980</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44496</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>45980</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45140</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45985</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45751</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>46157</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>45793</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>45338</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>46157</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>45041</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44824</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>46162</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>44774</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>46163</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45034</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>46163</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>46163</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>46162</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45995</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>44834</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>44803</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45593</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>46006</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>44888</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>46009</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>46008</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>46008</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>46008</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>46009</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>46010</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>46010</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>46168</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44842</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>45037</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>46168</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>46168</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45540</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45188</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45470</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45937</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>46027</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>46171</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45021</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>46171</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>46174</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>46174</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>46174</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>46038</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46174</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>46174</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>45484</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>46045</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45012</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>46176</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>46176</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>46176</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>46176</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>46051</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>44995</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>46176</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45408</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>46176</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>45938</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44950</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>46057</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45481</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45173</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>46072</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>46182</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44741</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>44748</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46184</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45545</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45014</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>46184</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45611</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>46084</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>46184</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>46184</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45319</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>45224</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>44882</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>45420</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>46090</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46090</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45625</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>45377</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45163</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>45206</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>45193</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>44782</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>46094</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45420</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>46098</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>46098</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>46098</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>46100</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>46100</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>46101</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>46101</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>46101</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>46101</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>46104</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35391,7 +35391,7 @@
         <v>46101</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45372</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>46104</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>46101</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>45735</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>46051</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44790</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>46178</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45109</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>46199</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>46113</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>45490</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>46113</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>46199</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>46119</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>46119</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>46122</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>46122</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45600</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>46122</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>46202</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36984,7 +36984,7 @@
         <v>46202</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>46202</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>46122</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44966</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44966</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>46122</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>45239</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>46126</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>45033</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44813</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>46202</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>46129</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>46127</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>46127</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>46199</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>46134</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>45163</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45757</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38363,7 +38363,7 @@
         <v>46203</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>45154</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>45477</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>46251</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38665,7 +38665,7 @@
         <v>45106</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>46206</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>44893</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45758</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>45018</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>46206</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>45308</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>46206</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>46206</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>46206</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45153</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>45968</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>45901</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>46210</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39752,7 +39752,7 @@
         <v>46210</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45601</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39908,7 +39908,7 @@
         <v>46253</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45477</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45751</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45191</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>46255</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45644</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>46191</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45188</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45014</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>46212</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>44886</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>46153</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>45766</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>44508</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45092</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>45131</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45747</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45397</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>44966</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45250</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45572</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44916</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>46267</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>46267</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>46223</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>46223</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>46267</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>46267</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>44726</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>46267</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>46267</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>46267</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46223</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>46268</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45986</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>46268</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>46268</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45777</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>45777</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>45562</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>46127</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>46275</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45463</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45572</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>46176</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45446</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45600</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>46174</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45607</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>46239</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>45559</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45600</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>46239</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>46239</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45503</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>46241</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>46283</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44189,7 +44189,7 @@
         <v>45527</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
         <v>45594</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>46282</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>46241</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45796</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>46240</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45664</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>45797</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>45457</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45578</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>45800</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45804</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>45764</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45178,7 +45178,7 @@
         <v>45819</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45832</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45833</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45833</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45480,7 +45480,7 @@
         <v>45840</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45842</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>45846</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45846</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45846</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45846</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45848</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
         <v>45784</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45861</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46162,7 +46162,7 @@
         <v>45747</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45867</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>44776</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46386,7 +46386,7 @@
         <v>44792</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46464,7 +46464,7 @@
         <v>45522</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44888</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45575</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>44609</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46771,7 +46771,7 @@
         <v>45607</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>44517</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>44517</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>45540</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>44517</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44686</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45867</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>45867</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45891</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45945</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45945</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         <v>45947</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45947</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45947</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45947</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45947</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45985</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>46162</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48175,7 +48175,7 @@
         <v>46199</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>

--- a/Översikt SMEDJEBACKEN.xlsx
+++ b/Översikt SMEDJEBACKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45629</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45869</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45517</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>44859</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>45967</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>46174</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>44823</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45001</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45862</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>45609</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45049</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45862</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45453</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45644</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45251</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45391</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>46009</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>46155</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45723</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>46283</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>44701</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44829</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45063</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>45454</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45063</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45763</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45607</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>46163</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>44482</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45720</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>46085</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44792</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>45723</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45441</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45698</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>45579</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44476</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>45064</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>45565</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>45975</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>46129</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45999</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>45401</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>46140</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45540</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>45225</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>46162</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>45109</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>46199</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>46199</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>45225</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45433</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45226</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44826</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45517</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>44727</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>45723</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>46282</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>46282</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45726</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>45786</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45527</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>45786</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44585</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>45642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45251</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>46029</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>46282</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44613</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44787</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>44691</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44496</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44641</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>44713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44706</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44496</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44475</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44826</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>44537</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44563</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44563</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44791</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44467</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44496</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44656</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44509</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44525</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44734</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44608</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44790</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44799</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>44496</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44496</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44778</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44784</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>44630</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>44803</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>44714</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44496</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>44861</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44811</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44876</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>44545</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>44469</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>44574</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44770</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44787</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44787</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44531</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44791</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44581</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44831</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44824</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45338</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45412</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45397</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>45219</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45401</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44860</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44883</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44741</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44809</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45429</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45420</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>45378</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45420</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45250</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45109</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44496</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45226</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>44859</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45467</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45454</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45462</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45446</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45884</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45937</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45019</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>46027</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45594</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45125</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45796</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>45527</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45484</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45477</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>44882</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45664</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44477</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>44895</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45797</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45503</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45578</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45457</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45012</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45887</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>45154</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45175</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45481</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45469</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45420</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>46038</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45891</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45891</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45891</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>45891</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45891</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>45371</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45800</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44909</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>46045</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45172</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45903</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>46051</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>45907</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45208</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45644</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>45021</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>46057</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45615</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45490</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45919</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45922</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45804</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44914</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44914</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45925</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>46072</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44916</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45372</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45931</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>46084</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44666</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45936</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45936</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>45936</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>45936</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45935</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>46090</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>46090</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45558</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>46094</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45938</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>46098</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45153</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>46098</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>45945</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45945</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>46098</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>46101</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>46101</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>46101</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>44718</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45946</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>46100</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>46100</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45945</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>46101</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>46101</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>46101</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>46104</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45947</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45947</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45947</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45950</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46104</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45947</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45947</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45947</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45947</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45947</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45950</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45950</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>46051</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45950</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45952</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45952</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>44950</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44496</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45953</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>45954</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44834</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>45919</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45310</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>46113</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45958</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>46113</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>44515</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45319</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45957</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45960</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>46119</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>46119</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45887</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45006</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45319</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45964</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45887</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45964</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45964</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>46122</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>46122</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>46122</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>46122</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>46122</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>46127</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>46127</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>46126</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45743</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45082</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>44897</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45971</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45407</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45246</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45973</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45973</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>45975</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>46129</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>45980</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45611</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>46134</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45980</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45980</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45985</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45600</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>45793</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>46136</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>44776</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>44782</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44803</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45995</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45140</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45757</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45188</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45428</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>44813</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>44477</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45188</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45224</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>46006</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45033</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45579</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45818</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>46008</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>46008</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45478</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>46008</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>46010</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>46009</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>46010</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>46009</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>44842</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>45193</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>45205</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>45163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45819</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45173</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45747</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>46141</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>46036</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>45735</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>45063</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>45603</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>44659</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>46141</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45124</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>46146</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>46146</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45832</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45014</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>46150</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>46150</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>46150</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>46149</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>46149</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>44503</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44890</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45229</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45833</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45833</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>44896</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>46155</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45751</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>46157</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>44855</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>46157</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45758</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46162</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46162</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45840</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45154</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45842</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>46163</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>46163</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>44482</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>44482</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>45846</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>45582</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>45846</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45846</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45846</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>46163</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45848</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45784</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>46168</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>46168</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>46168</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45107</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>46171</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>45861</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>46171</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45469</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>46174</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>46174</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>46174</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45037</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>46176</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45522</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>46176</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>45429</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45477</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45747</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>44776</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45601</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>46174</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>45106</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>44792</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>46176</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>46176</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>44475</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45867</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>46176</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>45424</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>44888</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
         <v>46176</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>44568</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>45938</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>46184</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>46184</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45429</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45575</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>46182</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>46184</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>46184</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44987</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45593</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45163</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>46178</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>45377</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>46199</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>46199</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>46199</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>46202</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45106</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45625</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>46202</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45191</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45501</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>44748</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>45589</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>46203</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>46202</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>46202</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>45670</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>45901</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>46206</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>46206</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>46206</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>44686</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>46251</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>46206</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>46206</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45092</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45751</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44876</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>46253</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>46210</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>46191</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>46212</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44734</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45428</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>46210</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45700</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>46255</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44845</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>44683</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>44683</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44617</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>45198</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>46153</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45698</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>44700</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45162</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>45250</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45206</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>45208</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45463</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>44726</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>45408</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>46223</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>46223</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>46223</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40425,7 +40425,7 @@
         <v>46267</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>46268</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>46268</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>46267</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>46267</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>46267</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>46267</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>46267</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>46267</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>44966</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>44966</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>46268</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>45986</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>44774</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>44790</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45018</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>44937</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>46275</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45077</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>44895</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>44494</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>44508</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45462</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45462</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45308</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45470</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>46240</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>46239</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>46239</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46239</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>46282</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>46241</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>46283</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>46286</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>46286</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>46286</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>46286</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>46286</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>46286</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>46241</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45545</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>46286</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>46283</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>46283</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>44888</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>44473</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45572</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>44778</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>44966</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>44966</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>46288</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>46283</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>46288</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>46176</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45968</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>46290</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>46174</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>45596</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>46127</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45034</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45106</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>44914</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>45471</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45625</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>44886</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45041</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>44995</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45131</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>44893</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>45766</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45540</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>45014</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45751</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45758</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>44630</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>44683</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>45153</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>45063</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>45121</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>45239</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45527</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45644</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>45264</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>45777</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>45777</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>45562</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>45446</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>45572</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>45463</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45600</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45559</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45607</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45600</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>44609</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>44686</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45607</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>44517</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>44517</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45540</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47897,7 +47897,7 @@
         <v>44517</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45867</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48053,7 +48053,7 @@
         <v>45867</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45891</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45945</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45945</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45947</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45947</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>45947</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45947</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>45947</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48755,7 +48755,7 @@
         <v>45985</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>46162</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>46199</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>

--- a/Översikt SMEDJEBACKEN.xlsx
+++ b/Översikt SMEDJEBACKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45629</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45869</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45517</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>44859</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>45967</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>46174</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>44823</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45001</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45862</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>45609</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45049</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45862</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45453</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45644</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45251</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45391</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>46009</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>46155</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45723</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>46283</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>44701</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44829</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45063</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>45454</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45063</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45763</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45607</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>46163</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>44482</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45720</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>46085</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44792</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>45723</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45441</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45698</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>45579</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44476</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>45064</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>45565</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>45975</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>46129</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45999</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>45401</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>46140</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45540</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>45225</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>46162</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>45109</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>46199</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>46199</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>45225</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45433</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45226</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44826</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45517</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>44727</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>45723</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>46282</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>46282</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45726</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>45786</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45527</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>45786</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44585</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>45642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45251</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>46029</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>46282</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44613</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44787</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>44691</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44496</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44641</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>44713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44706</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44496</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44475</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44826</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>44537</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44563</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44563</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44791</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44467</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44496</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44656</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44509</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44525</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44734</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44608</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44790</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44799</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>44496</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44496</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44778</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44784</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>44630</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>44803</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>44714</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44496</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>44861</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44811</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44876</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>44545</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>44469</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>44574</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44770</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44787</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44787</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44531</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44791</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44581</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44831</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44824</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45338</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45412</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45397</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>45219</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45401</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44860</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44883</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44741</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44809</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45429</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45420</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>45378</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45420</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45250</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45109</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44496</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45226</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>44859</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45467</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45454</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45462</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45446</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45884</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45937</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45019</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>46027</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45594</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45125</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45796</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>45527</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45484</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45477</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>44882</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45664</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44477</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>44895</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45797</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45503</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45578</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45457</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45012</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45887</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>45154</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45175</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45481</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45469</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45420</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>46038</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45891</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45891</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45891</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>45891</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45891</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>45371</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45800</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44909</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>46045</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45172</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45903</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>46051</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>45907</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45208</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45644</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>45021</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>46057</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45615</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45490</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45919</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45922</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45804</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44914</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44914</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45925</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>46072</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44916</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45372</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45931</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>46084</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44666</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45936</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45936</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>45936</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>45936</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45935</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>46090</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>46090</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45558</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>46094</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45938</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>46098</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45153</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>46098</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>45945</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45945</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>46098</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>46101</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>46101</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>46101</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>44718</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45946</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>46100</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>46100</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45945</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>46101</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>46101</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>46101</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>46104</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45947</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45947</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45947</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45950</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46104</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45947</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45947</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45947</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45947</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45947</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45950</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45950</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>46051</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45950</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45952</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45952</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>44950</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44496</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45953</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>45954</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44834</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>45919</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45310</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>46113</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45958</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>46113</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>44515</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45319</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45957</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45960</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>46119</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>46119</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45887</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45006</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45319</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45964</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45887</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45964</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45964</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>46122</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>46122</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>46122</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>46122</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>46122</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>46127</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>46127</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>46126</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45743</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45082</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>44897</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45971</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45407</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45246</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45973</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45973</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>45975</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>46129</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>45980</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45611</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>46134</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45980</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45980</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45985</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45600</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>45793</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>46136</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>44776</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>44782</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44803</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45995</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45140</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45757</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45188</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45428</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>44813</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>44477</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45188</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45224</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>46006</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45033</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45579</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45818</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>46008</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>46008</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45478</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>46008</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>46010</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>46009</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>46010</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>46009</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>44842</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>45193</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>45205</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>45163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45819</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45173</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45747</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>46141</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>46036</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>45735</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>45063</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>45603</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>44659</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>46141</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45124</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>46146</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>46146</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45832</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45014</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>46150</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>46150</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>46150</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>46149</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>46149</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>44503</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44890</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45229</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45833</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45833</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>44896</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>46155</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45751</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>46157</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>44855</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>46157</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45758</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46162</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46162</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45840</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45154</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45842</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>46163</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>46163</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>44482</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>44482</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>45846</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>45582</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>45846</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45846</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45846</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>46163</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45848</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45784</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>46168</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>46168</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>46168</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45107</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>46171</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>45861</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>46171</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45469</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>46174</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>46174</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>46174</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45037</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>46176</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45522</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>46176</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>45429</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45477</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45747</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>44776</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45601</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>46174</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>45106</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>44792</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>46176</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>46176</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>44475</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45867</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>46176</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>45424</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>44888</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
         <v>46176</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>44568</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>45938</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>46184</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>46184</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45429</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45575</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>46182</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>46184</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>46184</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44987</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45593</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45163</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>46178</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>45377</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>46199</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>46199</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>46199</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>46202</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45106</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45625</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>46202</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45191</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45501</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>44748</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>45589</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>46203</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>46202</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>46202</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>45670</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>45901</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>46206</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>46206</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>46206</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>44686</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>46251</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>46206</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>46206</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45092</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45751</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44876</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>46253</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>46210</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>46191</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>46212</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44734</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45428</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>46210</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45700</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>46255</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44845</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>44683</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>44683</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44617</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>45198</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>46153</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45698</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>44700</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45162</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>45250</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45206</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>45208</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45463</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>44726</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>45408</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>46223</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>46223</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>46223</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40425,7 +40425,7 @@
         <v>46267</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>46268</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>46268</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>46267</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>46267</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>46267</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>46267</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>46267</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>46267</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>44966</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>44966</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>46268</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>45986</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>44774</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>44790</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45018</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>44937</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>46275</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45077</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>44895</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>44494</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>44508</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45462</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45462</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45308</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45470</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>46240</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>46239</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>46239</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46239</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>46282</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>46241</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>46283</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>46286</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>46286</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>46286</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>46286</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>46286</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>46286</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>46241</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45545</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>46286</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>46283</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>46283</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>44888</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>44473</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45572</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>44778</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>44966</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>44966</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>46288</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>46283</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>46288</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>46176</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45968</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>46290</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>46174</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>45596</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>46127</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45034</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45106</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>44914</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>45471</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45625</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>44886</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45041</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>44995</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45131</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>44893</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>45766</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45540</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>45014</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45751</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45758</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>44630</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>44683</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>45153</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>45063</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>45121</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>45239</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45527</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45644</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>45264</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>45777</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>45777</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>45562</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>45446</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>45572</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>45463</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45600</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45559</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45607</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45600</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>44609</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>44686</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45607</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>44517</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>44517</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45540</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47897,7 +47897,7 @@
         <v>44517</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45867</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48053,7 +48053,7 @@
         <v>45867</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45891</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45945</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45945</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45947</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45947</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>45947</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45947</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>45947</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48755,7 +48755,7 @@
         <v>45985</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>46162</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>46199</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>

--- a/Översikt SMEDJEBACKEN.xlsx
+++ b/Översikt SMEDJEBACKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45629</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45869</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>45517</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>44823</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45001</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>44859</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45967</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46174</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45862</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>45609</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45723</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>46204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45862</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45453</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45644</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45251</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45391</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>45553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44701</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44829</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45454</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45607</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45763</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>44482</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45063</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>45063</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45720</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>46085</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44792</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45786</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45698</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45064</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45540</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45225</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45225</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45975</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44826</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>45999</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>46129</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>45401</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>46140</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>45726</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>46162</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44623</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45433</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>46199</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>46199</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45723</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>44476</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>45565</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>46282</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>46282</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45226</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>45441</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>45109</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45579</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>45517</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>45723</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45527</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45786</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>45517</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45642</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>46029</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>46282</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44613</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44787</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>44496</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>44691</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>44641</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44706</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44496</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>44832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44475</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>44826</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44537</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44563</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>44563</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>44791</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>44496</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44509</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>44734</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>44608</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>44790</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>44496</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44496</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44804</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44778</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>44784</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>44630</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>44803</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>44714</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>44496</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44861</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>44811</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44545</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>44574</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>44787</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44787</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44770</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>44531</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44581</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44791</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44831</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45429</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45469</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45153</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45462</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>44718</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>44876</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45107</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45527</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>44855</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45205</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>44515</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45219</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>44683</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45559</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45887</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>44700</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45019</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44496</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44914</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>44776</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45175</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>46006</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>46009</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>46008</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>46008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>46008</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45172</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45884</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>46009</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45600</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45310</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45501</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>46010</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>46010</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>44860</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45615</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44568</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>45891</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45891</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>44809</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>44895</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45891</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45891</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45937</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45891</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45420</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>46027</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>45670</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>44914</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>44914</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45424</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45903</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44482</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>44482</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>44909</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44859</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>46038</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45907</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>44987</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45503</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>46045</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45446</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45527</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45594</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>45796</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>45664</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45797</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44477</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>45457</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>46051</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45578</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45919</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45800</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45804</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45264</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45644</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44630</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45925</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>46057</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>45698</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45558</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45006</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45931</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45935</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45936</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45936</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>45936</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45936</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45938</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45429</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>46072</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>45945</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45945</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45945</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45154</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45947</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>45947</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45947</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45946</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45947</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45947</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45947</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45947</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45947</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45950</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45758</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45950</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45950</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>46084</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45250</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45953</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45208</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45229</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45952</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45952</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45957</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45919</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45954</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>46090</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45958</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>46090</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45960</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>45887</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45887</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45964</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>45964</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45964</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45371</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45743</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>46094</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>44617</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45971</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>46098</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>46098</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45582</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>46098</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46100</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>44683</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44683</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>46100</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>45973</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45973</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44494</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45378</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>44890</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>46101</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>46101</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>46101</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>46101</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>46104</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>46101</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45319</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>45975</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>46104</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>46101</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44473</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45764</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>46051</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>45980</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>45980</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>44734</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>45980</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45463</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45985</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>45407</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>46113</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>45793</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>45063</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>46113</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45819</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>46119</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>46119</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45700</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44937</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>46122</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>46122</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>46122</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46122</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>46122</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>45063</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>46126</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45467</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>45995</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>44477</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>46129</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>46127</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>46127</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>45124</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45162</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45832</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>45833</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>45833</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>46134</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45082</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45163</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>45454</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45757</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45840</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45751</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45842</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45846</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>45106</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45846</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45846</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45846</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45848</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45428</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>45429</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45784</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45818</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45401</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45589</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45077</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45579</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>46136</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>45471</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45198</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>45125</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45861</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>44659</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45412</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>44883</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45121</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45246</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>46141</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46141</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45747</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>44895</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45867</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>44776</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45478</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45596</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45603</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45747</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44792</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45522</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44888</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>44475</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46036</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>44897</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45575</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32065,7 +32065,7 @@
         <v>44896</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45462</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45462</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>46146</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>46146</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>44778</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45625</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>46149</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>46149</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>46150</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>44666</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>46150</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>46150</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>46155</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45106</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>45428</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>46157</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>44845</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>46157</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>44686</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>44503</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>46162</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>46163</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45208</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>46163</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>46163</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>46162</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44966</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>45226</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>44496</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45140</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>46168</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45751</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>46168</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>45338</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>46171</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>46171</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>46174</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>46174</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>46174</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>46174</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46174</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45041</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>46176</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>46176</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>46176</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>46176</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>46176</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>46176</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45938</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45469</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44824</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>44774</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45034</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>46182</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>46184</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46184</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>46184</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>46184</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>44834</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44803</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>45593</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44888</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>44842</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45037</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>46178</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>45540</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>46199</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>45188</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45470</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>46199</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>46202</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>46202</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>46202</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>46202</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>46199</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>46203</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>45021</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>46206</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>46206</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>46206</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
         <v>46206</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>46206</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>45901</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>46210</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>46210</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>46191</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>46212</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45484</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45012</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>46153</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>44995</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>45408</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>44950</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>46267</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>46267</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>46223</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>46223</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>45481</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>46267</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>46267</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45173</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>46267</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>46267</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>46267</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>46223</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>46268</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45986</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>46268</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>46268</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>44741</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>44748</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>45545</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45014</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45611</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>45319</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>45224</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40994,7 +40994,7 @@
         <v>46275</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>44882</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41145,7 +41145,7 @@
         <v>46239</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45420</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>46239</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>45625</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>46239</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45377</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>45163</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>45206</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>45193</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>46241</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>44782</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>46283</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>46282</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>46240</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45420</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         <v>45372</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42368,7 +42368,7 @@
         <v>46283</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45735</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>46283</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46286</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>46286</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>46283</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>46286</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>46286</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>44790</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>46286</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>46286</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45109</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         <v>46286</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45490</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>46127</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>45600</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>46288</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>46288</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>44966</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43810,7 +43810,7 @@
         <v>44966</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43883,7 +43883,7 @@
         <v>45968</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>45239</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>46174</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45033</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>44813</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46290</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>46176</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>46251</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>46297</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>46241</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45154</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>46297</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45477</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>46296</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44955,7 +44955,7 @@
         <v>45106</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>46255</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>44893</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45758</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45018</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>46253</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45308</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>46297</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         <v>45153</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>45601</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45477</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45751</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45191</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45644</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45188</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46115,7 +46115,7 @@
         <v>45014</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46188,7 +46188,7 @@
         <v>44886</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45766</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>44508</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>45092</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>45131</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45397</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>44966</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>45250</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45572</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>44916</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>44726</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>45777</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>45777</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45562</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>45463</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47308,7 +47308,7 @@
         <v>45572</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45446</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45600</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>44609</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45607</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>44517</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>44517</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45540</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44517</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>44686</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45867</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45867</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45891</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45945</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45945</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48473,7 +48473,7 @@
         <v>45947</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48551,7 +48551,7 @@
         <v>45947</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48629,7 +48629,7 @@
         <v>45947</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45947</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>45947</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48863,7 +48863,7 @@
         <v>45985</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>46162</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>46199</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>

--- a/Översikt SMEDJEBACKEN.xlsx
+++ b/Översikt SMEDJEBACKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45629</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45869</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>45517</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>44823</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45001</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>44859</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45967</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46174</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45862</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>45609</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45723</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>46204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45862</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45453</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45644</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45251</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45391</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>45553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44701</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44829</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45454</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45607</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45763</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>44482</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45063</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>45063</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45720</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>46085</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44792</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45786</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45698</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45064</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45540</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45225</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45225</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45975</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44826</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>45999</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>46129</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>45401</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>46140</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>45726</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>46162</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44623</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45433</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>46199</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>46199</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45723</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>44476</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>45565</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>46282</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>46282</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45226</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>45441</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>45109</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45579</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>45517</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>45723</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45527</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45786</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>45517</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45642</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>46029</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>46282</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44613</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44787</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>44496</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>44691</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>44641</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44706</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44496</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>44832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44475</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>44826</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44537</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44563</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>44563</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>44791</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>44496</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44509</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>44734</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>44608</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>44790</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>44496</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44496</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44804</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44778</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>44784</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>44630</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>44803</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>44714</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>44496</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44861</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>44811</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44545</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>44574</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>44787</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44787</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44770</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>44531</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44581</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44791</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44831</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45429</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45469</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45153</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45462</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>44718</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>44876</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45107</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45527</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>44855</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45205</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>44515</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45219</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>44683</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45559</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45887</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>44700</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45019</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44496</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44914</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>44776</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45175</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>46006</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>46009</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>46008</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>46008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>46008</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45172</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45884</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>46009</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45600</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45310</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45501</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>46010</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>46010</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>44860</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45615</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44568</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>45891</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45891</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>44809</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>44895</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45891</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45891</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45937</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45891</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45420</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>46027</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>45670</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>44914</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>44914</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45424</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45903</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44482</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>44482</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>44909</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44859</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>46038</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45907</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>44987</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45503</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>46045</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45446</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45527</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45594</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>45796</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>45664</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45797</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44477</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>45457</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>46051</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45578</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45919</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45800</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45804</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45264</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45644</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44630</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45925</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>46057</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>45698</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45558</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45006</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45931</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45935</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45936</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45936</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>45936</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45936</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45938</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45429</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>46072</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>45945</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45945</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45945</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45154</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45947</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>45947</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45947</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45946</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45947</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45947</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45947</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45947</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45947</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45950</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45758</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45950</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45950</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>46084</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45250</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45953</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45208</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45229</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45952</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45952</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45957</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45919</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45954</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>46090</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45958</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>46090</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45960</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>45887</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45887</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45964</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>45964</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45964</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45371</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45743</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>46094</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>44617</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45971</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>46098</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>46098</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45582</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>46098</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46100</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>44683</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44683</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>46100</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>45973</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45973</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44494</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45378</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>44890</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>46101</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>46101</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>46101</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>46101</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>46104</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>46101</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45319</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>45975</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>46104</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>46101</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44473</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45764</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>46051</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>45980</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>45980</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>44734</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>45980</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45463</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45985</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>45407</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>46113</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>45793</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>45063</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>46113</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45819</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>46119</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>46119</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45700</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44937</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>46122</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>46122</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>46122</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46122</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>46122</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>45063</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>46126</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45467</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>45995</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>44477</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>46129</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>46127</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>46127</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>45124</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45162</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45832</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>45833</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>45833</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>46134</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45082</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45163</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>45454</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45757</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45840</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45751</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45842</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45846</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>45106</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45846</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45846</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45846</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45848</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45428</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>45429</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45784</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45818</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45401</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45589</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45077</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45579</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>46136</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>45471</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45198</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>45125</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45861</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>44659</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45412</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>44883</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45121</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45246</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>46141</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46141</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45747</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>44895</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45867</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>44776</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45478</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45596</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45603</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45747</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44792</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45522</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44888</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>44475</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46036</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>44897</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45575</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32065,7 +32065,7 @@
         <v>44896</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45462</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45462</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>46146</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>46146</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>44778</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45625</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>46149</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>46149</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>46150</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>44666</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>46150</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>46150</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>46155</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45106</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>45428</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>46157</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>44845</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>46157</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>44686</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>44503</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>46162</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>46163</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45208</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>46163</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>46163</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>46162</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44966</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>45226</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>44496</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45140</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>46168</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45751</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>46168</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>45338</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>46171</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>46171</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>46174</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>46174</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>46174</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>46174</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46174</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45041</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>46176</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>46176</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>46176</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>46176</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>46176</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>46176</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45938</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45469</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44824</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>44774</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45034</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>46182</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>46184</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46184</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>46184</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>46184</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>44834</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44803</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>45593</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44888</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>44842</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45037</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>46178</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>45540</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>46199</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>45188</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45470</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>46199</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>46202</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>46202</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>46202</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>46202</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>46199</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>46203</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>45021</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>46206</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>46206</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>46206</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
         <v>46206</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>46206</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>45901</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>46210</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>46210</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>46191</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>46212</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45484</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45012</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>46153</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>44995</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>45408</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>44950</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>46267</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>46267</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>46223</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>46223</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>45481</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>46267</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>46267</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45173</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>46267</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>46267</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>46267</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>46223</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>46268</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45986</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>46268</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>46268</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>44741</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>44748</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>45545</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45014</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45611</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>45319</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>45224</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40994,7 +40994,7 @@
         <v>46275</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>44882</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41145,7 +41145,7 @@
         <v>46239</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45420</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>46239</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>45625</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>46239</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45377</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>45163</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>45206</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>45193</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>46241</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>44782</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>46283</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>46282</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>46240</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45420</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         <v>45372</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42368,7 +42368,7 @@
         <v>46283</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45735</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>46283</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46286</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>46286</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>46283</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>46286</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>46286</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>44790</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>46286</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>46286</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45109</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         <v>46286</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45490</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>46127</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>45600</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>46288</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>46288</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>44966</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43810,7 +43810,7 @@
         <v>44966</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43883,7 +43883,7 @@
         <v>45968</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>45239</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>46174</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45033</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>44813</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46290</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>46176</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>46251</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>46297</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>46241</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45154</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>46297</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45477</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>46296</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44955,7 +44955,7 @@
         <v>45106</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>46255</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>44893</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45758</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45018</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>46253</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45308</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>46297</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         <v>45153</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>45601</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45477</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45751</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45191</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45644</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45188</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46115,7 +46115,7 @@
         <v>45014</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46188,7 +46188,7 @@
         <v>44886</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45766</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>44508</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>45092</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>45131</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45397</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>44966</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>45250</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45572</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>44916</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>44726</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>45777</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>45777</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45562</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>45463</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47308,7 +47308,7 @@
         <v>45572</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45446</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45600</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>44609</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45607</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>44517</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>44517</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45540</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44517</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>44686</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45867</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45867</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45891</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45945</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45945</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48473,7 +48473,7 @@
         <v>45947</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48551,7 +48551,7 @@
         <v>45947</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48629,7 +48629,7 @@
         <v>45947</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45947</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>45947</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48863,7 +48863,7 @@
         <v>45985</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>46162</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>46199</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>

--- a/Översikt SMEDJEBACKEN.xlsx
+++ b/Översikt SMEDJEBACKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45629</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45869</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45517</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>46283</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>44823</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45001</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>44859</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45967</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46174</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45609</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45862</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45723</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>46204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45644</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45862</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45453</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45251</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45391</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>46009</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>46155</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44701</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44829</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45063</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45454</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45063</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>44482</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>45763</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45607</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46163</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45720</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>46085</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44792</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45441</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45225</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45723</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>45109</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45726</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>45698</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>45786</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45527</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>45786</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45517</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>45579</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>45225</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>45064</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>45565</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>45433</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44623</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>45226</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>44826</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45517</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>44727</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>45723</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>45975</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45540</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45999</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>46129</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45401</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>46140</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>46162</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>46199</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>46199</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>46282</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>46282</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>46302</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>46303</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44585</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>45642</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>45251</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>46029</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46282</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44613</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44787</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44571</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>44735</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44809</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>44496</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44691</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44641</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>44861</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44713</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>44637</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44809</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>44706</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44876</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>44496</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44832</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44826</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44496</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>44804</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>44861</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44811</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44876</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44537</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>44778</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>44784</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44563</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44563</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>44791</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>44525</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44630</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>44734</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44803</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44714</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44608</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44790</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44496</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44770</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44656</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>44496</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>44787</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>44787</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>44509</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>44531</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>45338</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44581</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44791</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>45041</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>44860</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>45014</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>44809</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>44883</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44831</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44503</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>44890</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45429</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>45229</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>44995</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45131</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45219</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>44741</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44896</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45751</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>44855</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>44893</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>45420</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>45758</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45420</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45378</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44824</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45766</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45250</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45154</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45109</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44482</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>44482</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44496</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>45582</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>44859</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45397</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>45401</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>45540</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45467</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>45226</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45412</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45014</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45751</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>45758</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45454</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45462</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45884</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45446</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44630</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45107</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45019</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45887</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44683</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45175</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45125</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45153</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>45469</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45469</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45037</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45484</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45477</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>44882</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44895</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45429</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45477</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>45891</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45891</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45891</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45891</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45891</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45063</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45012</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45601</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45154</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45481</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45121</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45239</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45106</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45420</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45527</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45903</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45644</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45424</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45371</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45264</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44909</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45907</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44568</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45172</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45777</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45777</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45429</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45208</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45644</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45562</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45021</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45446</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44987</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45572</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45615</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45463</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45919</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45600</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45593</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45490</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45163</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45559</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>45607</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>45925</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21701,7 +21701,7 @@
         <v>44914</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>44914</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45600</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>44916</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>45372</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45377</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45594</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45931</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45796</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45527</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45664</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44666</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45106</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45625</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>45191</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45797</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45503</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45578</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45457</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45501</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44748</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45936</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45936</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45589</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45558</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45800</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45936</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>45936</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45935</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45670</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>45804</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>45153</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44718</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>44686</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45092</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>45751</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>45938</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>44950</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44496</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>44876</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>45945</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>45946</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44834</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45945</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44734</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45428</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45764</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>45310</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>45947</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>45947</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45947</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45950</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44515</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45319</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45947</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45947</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45700</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45947</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44845</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45947</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45006</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45319</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>45819</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45947</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45950</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>44683</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44683</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>44617</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45950</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45950</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45952</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45082</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45952</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>44897</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45832</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45198</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45953</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>45407</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45246</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45919</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45958</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45957</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45960</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45698</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45833</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45833</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>44700</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45887</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45964</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45887</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>45964</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45964</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45162</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45611</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>45840</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>45743</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45250</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45206</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45208</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45842</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45463</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>44726</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45408</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>45846</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>45600</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>45971</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>45846</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45846</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>45846</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>45848</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44776</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44782</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45784</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45973</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>44803</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45140</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45861</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>44966</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>44966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>44813</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45522</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45747</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44776</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>44792</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45867</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>44774</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45188</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>44888</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45224</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45980</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45033</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>44790</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45575</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45478</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>45980</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>45980</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44842</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>45193</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45205</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45018</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44937</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45173</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45077</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>46098</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>46098</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44895</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>46098</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>46101</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>44494</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>46101</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>46101</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44508</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>46100</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>46100</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>46101</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>46101</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>46101</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>46104</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>46104</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45462</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33967,7 +33967,7 @@
         <v>45462</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>46051</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45308</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45470</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45985</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>45735</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45063</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45793</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44659</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46113</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>46113</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>45124</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>46119</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46119</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45545</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>46122</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46122</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>46122</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>46122</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45995</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>46127</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>46127</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>46126</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44888</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>46129</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45572</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>44778</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>46134</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>44966</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44966</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>46006</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>46008</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>46008</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>46008</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>46010</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>46009</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>46010</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>46009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>46136</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45596</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45937</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45757</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>46027</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45428</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45034</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45106</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>45579</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>45818</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>46038</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45163</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>44914</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45471</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>46045</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45625</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45747</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>46141</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>44886</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>46036</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>46051</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>46057</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45603</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>46141</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>46146</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>46150</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>46150</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>46150</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>46149</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39081,7 +39081,7 @@
         <v>46149</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>46072</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>46084</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>46155</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>46157</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>46157</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>46090</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>46090</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>46162</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>46162</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>46094</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>46163</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>46163</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>46163</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>46168</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>46168</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>46168</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40377,7 +40377,7 @@
         <v>46171</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>46171</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>46174</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>46174</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>46174</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>46174</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>46176</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>46176</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>46174</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>46176</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         <v>46176</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>46176</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>46176</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>46184</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>46184</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>46182</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>46184</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>46184</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>46178</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>46199</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>46199</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>46199</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>46202</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>46202</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>46203</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>46202</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>46202</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45901</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>46206</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>46206</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>46206</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>46206</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>46191</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>46212</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>46210</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>46153</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46223</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>46223</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>46223</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>46267</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46268</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>46268</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>46267</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46267</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>46267</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>46267</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>46267</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>46267</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>46268</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45986</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>46275</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>46240</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>46239</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>46239</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>46239</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>46241</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>46283</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>46286</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>46286</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>46286</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>46286</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>46286</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>46286</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>46286</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>46283</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>46283</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>46288</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>46283</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>46288</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         <v>46176</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45820,7 +45820,7 @@
         <v>45968</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>46290</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45976,7 +45976,7 @@
         <v>46174</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>46253</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>46296</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>46251</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>46297</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>46297</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45975</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>46297</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>46241</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>46255</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>46206</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46819,7 +46819,7 @@
         <v>46127</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>46303</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>46303</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>44609</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47126,7 +47126,7 @@
         <v>44686</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45607</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>44517</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>44517</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47438,7 +47438,7 @@
         <v>45540</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>44517</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45867</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45867</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45891</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>45945</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45945</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>45947</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>45947</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48140,7 +48140,7 @@
         <v>45947</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45947</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45947</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45985</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>46162</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>46199</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>

--- a/Översikt SMEDJEBACKEN.xlsx
+++ b/Översikt SMEDJEBACKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45629</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45869</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45517</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>46283</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>44823</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45001</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>44859</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45967</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46174</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45609</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45862</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45723</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>46204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45644</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45862</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45453</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45251</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45391</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>46009</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>46155</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44701</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44829</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45063</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45454</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45063</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>44482</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>45763</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45607</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46163</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45720</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>46085</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44792</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45441</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45225</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45723</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>45109</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45726</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>45698</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>45786</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45527</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>45786</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45517</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>45579</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>45225</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>45064</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>45565</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>45433</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44623</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>45226</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>44826</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45517</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>44727</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>45723</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>45975</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45540</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45999</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>46129</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45401</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>46140</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>46162</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>46199</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>46199</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>46282</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>46282</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>46302</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>46303</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44585</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>45642</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>45251</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>46029</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46282</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44613</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44787</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44571</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>44735</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44809</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>44496</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44691</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44641</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>44861</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44713</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>44637</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44809</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>44706</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44876</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>44496</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44832</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44826</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44496</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>44804</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>44861</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44811</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44876</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44537</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>44778</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>44784</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44563</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44563</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>44791</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>44525</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44630</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>44734</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44803</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44714</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44608</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44790</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44496</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44770</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44656</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>44496</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>44787</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>44787</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>44509</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>44531</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>45338</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44581</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44791</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>45041</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>44860</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>45014</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>44809</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>44883</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44831</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44503</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>44890</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45429</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>45229</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>44995</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45131</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45219</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>44741</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44896</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45751</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>44855</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>44893</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>45420</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>45758</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45420</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45378</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44824</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45766</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45250</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45154</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45109</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44482</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>44482</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44496</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>45582</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>44859</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45397</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>45401</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>45540</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45467</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>45226</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45412</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45014</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45751</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>45758</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45454</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45462</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45884</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45446</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44630</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45107</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45019</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45887</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44683</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45175</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45125</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45153</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>45469</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45469</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45037</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45484</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45477</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>44882</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44895</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45429</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45477</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>45891</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45891</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45891</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45891</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45891</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45063</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45012</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45601</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45154</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45481</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45121</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45239</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45106</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45420</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45527</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45903</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45644</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45424</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45371</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45264</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44909</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45907</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44568</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45172</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45777</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45777</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45429</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45208</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45644</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45562</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45021</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45446</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44987</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45572</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45615</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45463</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45919</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45600</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45593</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45490</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45163</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45559</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>45607</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>45925</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21701,7 +21701,7 @@
         <v>44914</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>44914</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45600</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>44916</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>45372</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45377</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45594</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45931</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45796</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45527</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45664</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44666</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45106</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45625</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>45191</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45797</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45503</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45578</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45457</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45501</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44748</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45936</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45936</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45589</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45558</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45800</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45936</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>45936</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45935</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45670</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>45804</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>45153</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44718</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>44686</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45092</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>45751</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>45938</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>44950</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44496</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>44876</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>45945</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>45946</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44834</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45945</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44734</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45428</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45764</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>45310</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>45947</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>45947</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45947</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45950</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44515</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45319</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45947</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45947</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45700</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45947</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44845</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45947</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45006</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45319</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>45819</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45947</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45950</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>44683</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44683</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>44617</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45950</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45950</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45952</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45082</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45952</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>44897</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45832</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45198</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45953</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>45407</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45246</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45919</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45958</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45957</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45960</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45698</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45833</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45833</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>44700</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45887</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45964</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45887</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>45964</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45964</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45162</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45611</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>45840</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>45743</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45250</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45206</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45208</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45842</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45463</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>44726</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45408</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>45846</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>45600</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>45971</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>45846</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45846</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>45846</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>45848</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44776</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44782</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45784</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45973</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>44803</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45140</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45861</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>44966</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>44966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>44813</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45522</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45747</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44776</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>44792</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45867</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>44774</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45188</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>44888</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45224</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45980</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45033</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>44790</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45575</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45478</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>45980</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>45980</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44842</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>45193</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45205</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45018</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44937</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45173</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45077</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>46098</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>46098</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44895</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>46098</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>46101</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>44494</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>46101</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>46101</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44508</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>46100</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>46100</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>46101</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>46101</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>46101</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>46104</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>46104</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45462</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33967,7 +33967,7 @@
         <v>45462</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>46051</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45308</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45470</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45985</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>45735</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45063</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45793</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44659</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46113</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>46113</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>45124</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>46119</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46119</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45545</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>46122</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46122</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>46122</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>46122</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45995</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>46127</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>46127</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>46126</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44888</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>46129</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45572</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>44778</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>46134</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>44966</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44966</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>46006</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>46008</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>46008</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>46008</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>46010</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>46009</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>46010</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>46009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>46136</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45596</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45937</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45757</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>46027</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45428</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45034</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45106</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>45579</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>45818</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>46038</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45163</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>44914</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45471</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>46045</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45625</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45747</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>46141</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>44886</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>46036</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>46051</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>46057</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45603</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>46141</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>46146</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>46150</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>46150</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>46150</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>46149</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39081,7 +39081,7 @@
         <v>46149</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>46072</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>46084</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>46155</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>46157</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>46157</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>46090</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>46090</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>46162</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>46162</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>46094</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>46163</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>46163</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>46163</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>46168</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>46168</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>46168</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40377,7 +40377,7 @@
         <v>46171</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>46171</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>46174</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>46174</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>46174</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>46174</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>46176</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>46176</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>46174</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>46176</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         <v>46176</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>46176</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>46176</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>46184</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>46184</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>46182</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>46184</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>46184</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>46178</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>46199</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>46199</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>46199</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>46202</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>46202</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>46203</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>46202</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>46202</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45901</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>46206</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>46206</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>46206</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>46206</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>46191</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>46212</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>46210</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>46153</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46223</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>46223</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>46223</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>46267</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46268</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>46268</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>46267</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46267</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>46267</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>46267</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>46267</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>46267</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>46268</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45986</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>46275</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>46240</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>46239</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>46239</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>46239</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>46241</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>46283</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>46286</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>46286</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>46286</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>46286</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>46286</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>46286</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>46286</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>46283</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>46283</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>46288</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>46283</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>46288</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         <v>46176</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45820,7 +45820,7 @@
         <v>45968</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>46290</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45976,7 +45976,7 @@
         <v>46174</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>46253</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>46296</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>46251</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>46297</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>46297</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45975</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>46297</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>46241</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>46255</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>46206</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46819,7 +46819,7 @@
         <v>46127</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>46303</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>46303</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>44609</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47126,7 +47126,7 @@
         <v>44686</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45607</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>44517</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>44517</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47438,7 +47438,7 @@
         <v>45540</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>44517</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45867</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45867</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45891</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>45945</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45945</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>45947</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>45947</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48140,7 +48140,7 @@
         <v>45947</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45947</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45947</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45985</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>46162</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>46199</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>

--- a/Översikt SMEDJEBACKEN.xlsx
+++ b/Översikt SMEDJEBACKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45629</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45869</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>45517</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>44823</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45001</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>44859</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45967</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46174</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45609</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45862</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45723</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>46204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45453</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45644</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45862</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45251</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45391</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>45723</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>46009</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>45553</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>46155</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44701</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44829</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45607</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45763</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45454</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>45063</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45063</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45720</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>46085</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45064</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>45540</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>45225</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45225</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45698</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>46140</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45726</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>46162</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>45975</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44727</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>45999</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44623</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45433</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45723</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>46199</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>46199</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>46129</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>45565</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>45401</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45226</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45441</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45109</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>45579</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>46282</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>46282</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45723</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>45527</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>45786</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>45517</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>45786</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>46303</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>46302</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45642</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>46029</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>46282</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44613</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44787</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>44691</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44496</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44641</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>44713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44706</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>44496</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44826</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44537</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44563</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44563</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44791</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44496</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44656</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>44509</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44734</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44608</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>44790</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44496</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44496</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>44804</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>44778</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44784</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44630</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44803</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>44714</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>44496</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44861</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44811</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44876</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44545</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44574</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44787</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44787</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44770</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>44531</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44581</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>44791</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>44831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45429</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>45469</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45462</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>44876</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45153</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>44855</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44718</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45107</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45527</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>45205</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>44515</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45219</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44683</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44776</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>44496</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45172</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44914</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>44860</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44568</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45310</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45501</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45615</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>44700</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44809</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44895</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45420</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45670</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>44914</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>44914</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>44909</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>45424</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>44859</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>44987</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45446</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45019</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45264</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45644</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44630</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>45698</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>45429</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45154</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45250</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45758</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45208</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45229</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>45558</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>45006</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45371</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44617</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>45582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45378</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44683</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44683</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44890</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44494</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45319</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44734</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45407</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45463</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45175</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45063</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45884</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45428</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45700</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44937</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45818</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>45063</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45579</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45467</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>46136</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45469</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45891</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45891</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45891</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45891</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45891</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45124</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45162</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45887</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46141</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>46141</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45603</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45747</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45082</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45903</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45454</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45907</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>46036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45751</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45919</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>46146</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45106</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>46146</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>45922</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>46149</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45925</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45429</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>46149</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45401</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45589</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45931</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45935</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45936</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45077</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45936</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45936</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>45936</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>46150</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>46150</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>46150</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45471</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45938</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45198</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45945</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45945</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>45125</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>44659</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>46155</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45412</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44883</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45945</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45947</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>45947</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45947</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45121</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45946</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45246</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45947</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45947</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45947</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45947</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45947</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45950</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45950</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45950</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45950</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45953</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45952</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45952</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45957</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>45919</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44895</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>46157</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45958</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>46157</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45478</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45596</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45960</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45887</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>45887</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45964</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45964</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45964</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45743</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44897</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45971</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>44896</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45462</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45462</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45973</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>46162</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>46163</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>44778</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45625</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>46163</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>46163</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>46162</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45980</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45980</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>45980</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>44666</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45985</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45106</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45793</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45428</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44845</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44686</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44503</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>46168</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>45208</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>45995</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44966</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>45226</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>46168</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>46168</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>44496</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>46171</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45140</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>46171</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>46174</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45751</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45338</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>46006</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>46009</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28166,7 +28166,7 @@
         <v>46008</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>46008</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>46008</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>46174</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>46009</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>46010</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>46174</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45041</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>46010</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>46174</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>46174</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44824</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44774</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45937</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>46027</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>46176</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>46176</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45034</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>46176</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>46176</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>46176</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>46176</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>46038</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>44834</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44803</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>46045</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>45593</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44888</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>46051</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>46182</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>46057</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44842</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>46184</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>46184</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45037</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45540</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>46184</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46184</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45188</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>45470</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>46072</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45021</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>46084</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>46090</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>46090</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45484</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>46094</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45012</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>46098</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>46098</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>46098</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>46100</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>46100</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>46101</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>46101</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>46101</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>46101</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>44995</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>46104</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>46101</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45408</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>46104</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>46101</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>44950</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>46051</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>46113</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>46113</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>46178</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>46119</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>46199</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33496,7 +33496,7 @@
         <v>46119</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>45481</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45173</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>46122</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>46122</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>46122</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>46122</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>46202</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>46202</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>46202</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>46126</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>46202</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>46129</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>44741</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>46127</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>46127</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>46199</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44748</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45545</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35031,7 +35031,7 @@
         <v>45014</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>45611</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>45319</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>46134</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>45224</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>46203</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45163</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45757</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>44882</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45420</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>46206</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45625</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45377</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36015,7 +36015,7 @@
         <v>45163</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>45206</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45193</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>46206</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>44782</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36400,7 +36400,7 @@
         <v>46206</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>46206</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45420</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45901</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>46191</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45372</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>46212</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>45735</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>46153</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>44790</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>45109</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>45490</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>46223</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>46223</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>46223</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45600</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>44966</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44966</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45239</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45033</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44813</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>46275</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>46239</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46239</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>46239</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45154</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>46241</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>46283</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45477</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>46282</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>46240</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45106</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>44893</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45758</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>45018</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45308</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>46283</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>45153</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>46283</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>46286</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>46286</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>46283</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>46286</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>46286</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>46286</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45601</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45477</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>46286</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45751</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45191</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>45644</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45188</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>45014</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>46288</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>46288</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>44886</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>45968</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>46174</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>46290</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45766</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>44508</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>45092</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>45131</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>46176</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45397</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>44966</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>46251</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45250</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45572</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44916</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>46297</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>46241</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>46297</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>44726</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>46296</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>46255</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>46253</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46297</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45975</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>45777</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45777</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45562</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>45463</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>45572</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45446</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45600</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>46303</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45607</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>46303</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43230,7 +43230,7 @@
         <v>45559</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>45600</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45503</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45527</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45594</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43605,7 +43605,7 @@
         <v>45796</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45664</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>45797</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>46210</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>45457</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>46206</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45578</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45800</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>45804</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>46308</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>46308</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>46127</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>45986</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>46268</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>46268</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>46268</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>45764</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>46267</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>46267</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>46311</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>46267</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45819</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>46267</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>46267</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>46267</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>46267</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45832</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45651,7 +45651,7 @@
         <v>45833</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45833</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45840</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45842</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>45846</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45846</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45846</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46182,7 +46182,7 @@
         <v>45846</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>45848</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>45784</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>45861</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>45747</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>45867</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>44776</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>44792</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45522</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>44888</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45575</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>44609</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
         <v>45607</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>44517</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>44517</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47322,7 +47322,7 @@
         <v>45540</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>44517</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44686</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47556,7 +47556,7 @@
         <v>45867</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>45867</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45891</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45945</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45945</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45947</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45947</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48102,7 +48102,7 @@
         <v>45947</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45947</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>45947</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45985</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>46162</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>46199</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>

--- a/Översikt SMEDJEBACKEN.xlsx
+++ b/Översikt SMEDJEBACKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45629</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45869</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>45517</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>44823</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45001</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>44859</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45967</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46174</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45609</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45862</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45723</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>46204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45453</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45644</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45862</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45251</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45391</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>45723</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>46009</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>45553</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>46155</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44701</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44829</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45607</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45763</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45454</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>45063</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45063</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45720</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>46085</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45064</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>45540</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>45225</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45225</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45698</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>46140</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45726</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>46162</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>45975</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44727</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>45999</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44623</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45433</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45723</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>46199</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>46199</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>46129</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>45565</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>45401</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45226</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45441</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45109</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>45579</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>46282</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>46282</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45723</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>45527</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>45786</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>45517</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>45786</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>46303</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>46302</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45642</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>46029</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>46282</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44613</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44787</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>44691</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44496</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44641</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>44713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44706</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>44496</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44826</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44537</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44563</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44563</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44791</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44496</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44656</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>44509</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44734</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44608</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>44790</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44496</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44496</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>44804</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>44778</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44784</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44630</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44803</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>44714</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>44496</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44861</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44811</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44876</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44545</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44574</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44787</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44787</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44770</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>44531</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44581</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>44791</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>44831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45429</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>45469</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45462</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>44876</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45153</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>44855</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44718</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45107</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45527</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>45205</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>44515</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45219</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44683</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44776</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>44496</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45172</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44914</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>44860</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44568</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45310</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45501</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45615</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>44700</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44809</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44895</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45420</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45670</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>44914</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>44914</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>44909</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>45424</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>44859</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>44987</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45446</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45019</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45264</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45644</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44630</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>45698</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>45429</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45154</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45250</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45758</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45208</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45229</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>45558</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>45006</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45371</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44617</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>45582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45378</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44683</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44683</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44890</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44494</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45319</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44734</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45407</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45463</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45175</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45063</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45884</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45428</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45700</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44937</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45818</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>45063</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45579</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45467</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>46136</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45469</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45891</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45891</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45891</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45891</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45891</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45124</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45162</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45887</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46141</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>46141</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45603</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45747</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45082</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45903</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45454</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45907</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>46036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45751</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45919</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>46146</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45106</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>46146</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>45922</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>46149</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45925</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45429</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>46149</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45401</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45589</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45931</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45935</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45936</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45077</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45936</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45936</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>45936</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>46150</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>46150</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>46150</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45471</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45938</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45198</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45945</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45945</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>45125</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>44659</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>46155</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45412</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44883</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45945</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45947</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>45947</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45947</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45121</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45946</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45246</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45947</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45947</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45947</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45947</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45947</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45950</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45950</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45950</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45950</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45953</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45952</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45952</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45957</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>45919</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44895</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>46157</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45958</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>46157</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45478</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45596</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45960</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45887</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>45887</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45964</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45964</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45964</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45743</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44897</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45971</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>44896</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45462</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45462</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45973</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>46162</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>46163</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>44778</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45625</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>46163</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>46163</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>46162</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45980</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45980</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>45980</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>44666</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45985</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45106</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45793</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45428</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44845</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44686</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44503</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>46168</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>45208</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>45995</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44966</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>45226</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>46168</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>46168</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>44496</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>46171</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45140</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>46171</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>46174</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45751</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45338</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>46006</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>46009</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28166,7 +28166,7 @@
         <v>46008</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>46008</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>46008</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>46174</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>46009</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>46010</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>46174</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45041</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>46010</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>46174</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>46174</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44824</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44774</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45937</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>46027</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>46176</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>46176</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45034</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>46176</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>46176</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>46176</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>46176</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>46038</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>44834</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44803</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>46045</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>45593</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44888</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>46051</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>46182</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>46057</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44842</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>46184</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>46184</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45037</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45540</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>46184</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46184</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45188</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>45470</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>46072</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45021</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>46084</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>46090</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>46090</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45484</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>46094</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45012</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>46098</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>46098</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>46098</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>46100</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>46100</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>46101</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>46101</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>46101</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>46101</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>44995</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>46104</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>46101</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45408</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>46104</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>46101</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>44950</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>46051</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>46113</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>46113</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>46178</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>46119</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>46199</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33496,7 +33496,7 @@
         <v>46119</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>45481</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45173</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>46122</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>46122</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>46122</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>46122</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>46202</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>46202</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>46202</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>46126</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>46202</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>46129</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>44741</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>46127</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>46127</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>46199</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44748</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45545</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35031,7 +35031,7 @@
         <v>45014</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>45611</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>45319</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>46134</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>45224</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>46203</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45163</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45757</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>44882</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45420</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>46206</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45625</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45377</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36015,7 +36015,7 @@
         <v>45163</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>45206</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45193</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>46206</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>44782</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36400,7 +36400,7 @@
         <v>46206</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>46206</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45420</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45901</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>46191</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45372</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>46212</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>45735</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>46153</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>44790</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>45109</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>45490</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>46223</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>46223</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>46223</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45600</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>44966</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44966</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45239</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45033</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44813</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>46275</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>46239</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46239</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>46239</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45154</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>46241</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>46283</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45477</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>46282</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>46240</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45106</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>44893</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45758</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>45018</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45308</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>46283</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>45153</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>46283</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>46286</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>46286</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>46283</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>46286</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>46286</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>46286</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45601</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45477</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>46286</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45751</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45191</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>45644</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45188</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>45014</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>46288</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>46288</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>44886</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>45968</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>46174</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>46290</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45766</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>44508</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>45092</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>45131</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>46176</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45397</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>44966</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>46251</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45250</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45572</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44916</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>46297</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>46241</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>46297</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>44726</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>46296</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>46255</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>46253</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46297</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45975</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>45777</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45777</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45562</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>45463</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>45572</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45446</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45600</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>46303</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45607</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>46303</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43230,7 +43230,7 @@
         <v>45559</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>45600</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45503</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45527</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45594</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43605,7 +43605,7 @@
         <v>45796</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45664</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>45797</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>46210</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>45457</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>46206</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45578</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45800</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>45804</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>46308</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>46308</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>46127</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>45986</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>46268</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>46268</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>46268</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>45764</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>46267</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>46267</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>46311</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>46267</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45819</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>46267</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>46267</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>46267</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>46267</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45832</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45651,7 +45651,7 @@
         <v>45833</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45833</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45840</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45842</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>45846</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45846</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45846</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46182,7 +46182,7 @@
         <v>45846</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>45848</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>45784</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>45861</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>45747</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>45867</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>44776</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>44792</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45522</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>44888</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45575</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>44609</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
         <v>45607</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>44517</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>44517</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47322,7 +47322,7 @@
         <v>45540</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>44517</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44686</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47556,7 +47556,7 @@
         <v>45867</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>45867</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45891</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45945</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45945</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45947</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45947</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48102,7 +48102,7 @@
         <v>45947</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45947</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>45947</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45985</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>46162</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>46199</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>

--- a/Översikt SMEDJEBACKEN.xlsx
+++ b/Översikt SMEDJEBACKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45629</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45869</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>45517</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>44823</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45001</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>44859</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45967</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46174</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45862</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>45609</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45723</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45049</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45644</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45862</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45453</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45251</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45391</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46155</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>46009</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>45553</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45723</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44701</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44829</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46163</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>45063</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45454</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>45063</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45763</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45607</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45720</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>46085</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45698</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45723</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>46162</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>45441</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45726</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45975</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>46199</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46199</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45999</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45786</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45527</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>45786</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>46282</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>45517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>46282</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45792</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>46302</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>46303</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>46129</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45401</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>46140</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45579</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>45064</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45565</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45540</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45225</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45109</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>45225</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45433</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44623</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45226</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44826</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45517</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>44727</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>45723</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44585</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>45251</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>46029</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>46282</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44613</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44787</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>44691</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44496</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44641</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>44713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44706</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>44496</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44826</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44537</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44563</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44563</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44791</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44496</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44656</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>44509</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44734</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44608</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>44790</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44496</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44496</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>44804</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>44778</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44784</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44630</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44803</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>44714</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>44496</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44861</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44811</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44545</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44574</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44770</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44787</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44787</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>44531</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44581</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>44791</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45887</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45175</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44831</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>45469</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45219</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44741</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45891</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45891</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>45891</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>45891</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>45891</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>44824</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>45884</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45397</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45401</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45412</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45338</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45596</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45903</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44860</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45907</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>46162</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45034</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>46162</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45106</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>46163</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>46163</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>44809</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>46163</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45919</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>45922</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>46168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>46168</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>44883</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>46168</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45925</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>46171</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>46171</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45931</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>46174</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>46174</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>46174</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>46174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>44914</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45471</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>46176</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45936</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>45936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45936</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>45936</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45935</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>45429</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45625</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44886</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>46176</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45041</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45938</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>46174</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>46176</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>46176</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>45420</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>46176</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45945</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45945</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45420</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45378</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>46176</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45250</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45946</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45109</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>44496</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44859</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44995</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45947</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45947</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45947</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45131</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45947</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45947</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>45947</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45947</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45947</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>45950</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45950</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45950</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45952</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45952</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>46184</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>46184</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45953</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>46182</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44893</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>46184</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45919</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>46184</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45958</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45957</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45960</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45766</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45887</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45467</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45964</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45887</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45964</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45964</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45743</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45226</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45540</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45014</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45751</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45758</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45971</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>46178</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>45973</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>46199</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>46199</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>46199</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>46202</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44630</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45980</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>46202</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44683</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45980</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45980</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45153</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45454</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>46203</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>46202</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>46202</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45901</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45985</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>46206</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>45063</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>46206</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>46206</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>45793</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>46206</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45121</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45239</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>46191</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>46212</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45527</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45462</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45644</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45446</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45995</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>46153</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>45264</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>46223</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>46223</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>46223</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45777</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45777</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>46006</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45562</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45446</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>46008</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>46008</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>46008</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>46010</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46009</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>46010</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>46009</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>45572</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>45463</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45600</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45937</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45559</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>46240</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>46027</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45607</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>46239</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>46239</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>46239</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>46241</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>46283</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>46286</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>46286</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>46286</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>46286</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>46286</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>45019</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45600</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>46286</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>46038</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>46286</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45594</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>46283</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>46283</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45796</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>45527</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45664</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45797</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45503</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45578</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>45457</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>46045</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46288</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>46283</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>46288</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45800</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45125</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>46176</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>46051</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45804</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45968</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>46290</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>46057</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>46174</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45764</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>46072</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>46296</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45819</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45484</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45477</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>46251</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>44882</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45832</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>46084</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45833</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45833</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46297</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>46090</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>46090</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>46297</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45840</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>46094</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>45975</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>44895</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>46297</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>46098</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>45842</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>46098</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>46241</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45846</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>46098</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>46101</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>46101</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>46101</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>46255</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>46100</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>46100</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>46101</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>46101</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>46101</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>46104</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45846</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45846</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>45846</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>45012</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>46104</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32891,7 +32891,7 @@
         <v>45848</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>46051</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>45154</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45784</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33183,7 +33183,7 @@
         <v>45481</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>46113</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>45861</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>46113</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>46303</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>46303</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45522</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>45747</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>44776</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44792</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45420</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>46119</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>45867</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>46119</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44888</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>45575</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>46122</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>46122</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>46122</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>46122</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>46127</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>46127</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>46126</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>46129</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>46308</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45371</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>46210</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44909</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>46134</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45172</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>46308</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45208</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45644</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>46206</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45021</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>46268</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>46267</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>46136</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>46267</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>46267</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>46267</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>46268</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>46267</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>46267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>46267</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>45615</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>45986</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45757</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45490</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>46311</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>45428</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>46268</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>45579</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45818</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44914</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>44914</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>46316</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>46316</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>46316</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>46316</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>44916</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>46316</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>46316</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45163</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>46316</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>46316</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>45372</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>46275</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44666</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>45747</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>46141</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>46036</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45603</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>45558</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>46141</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>46127</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>46146</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45153</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>46150</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>46150</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>46150</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>46149</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>44718</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>46149</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>44950</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44496</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44834</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>46155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>45310</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>46157</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44515</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40164,7 +40164,7 @@
         <v>45319</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>46157</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45006</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>45319</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>45082</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>44897</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>45407</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45246</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45611</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45600</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>44776</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>44782</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>44803</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45140</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41201,7 +41201,7 @@
         <v>45188</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
         <v>44813</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>45188</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>45224</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45033</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>45478</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>44842</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>45193</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>45205</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>45173</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41956,7 +41956,7 @@
         <v>45735</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>45063</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>44659</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>45124</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>45014</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>44503</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44890</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45229</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>44896</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45751</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>44855</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45758</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45154</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45582</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45107</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45469</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45037</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>45429</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45477</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>45601</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>45106</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43534,7 +43534,7 @@
         <v>45424</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>44568</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45429</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>44987</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>45593</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45163</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>45377</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45106</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45625</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>45191</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>45501</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44377,7 +44377,7 @@
         <v>44748</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44450,7 +44450,7 @@
         <v>45589</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45670</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>44686</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45092</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>45751</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>44876</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>44734</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44976,7 +44976,7 @@
         <v>45428</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45700</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45122,7 +45122,7 @@
         <v>44845</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>44683</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>44683</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>44617</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45198</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45698</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>44700</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>45162</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45250</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45206</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45862,7 +45862,7 @@
         <v>45208</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45463</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>44726</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45408</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>44966</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>44966</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>44774</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>44790</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45018</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>44937</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>45077</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44895</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>44494</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>44508</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>45462</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45462</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45308</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>45470</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45545</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>44888</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>45572</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>44778</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44966</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>44966</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>44609</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>44686</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45607</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>44517</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>44517</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45540</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48102,7 +48102,7 @@
         <v>44517</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45867</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>45867</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45891</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>45945</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>45945</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48570,7 +48570,7 @@
         <v>45947</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45947</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45947</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48804,7 +48804,7 @@
         <v>45947</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45947</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>45985</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49038,7 +49038,7 @@
         <v>46162</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>46199</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>

--- a/Översikt SMEDJEBACKEN.xlsx
+++ b/Översikt SMEDJEBACKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45629</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45869</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>45517</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>44823</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45001</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>44859</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45967</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46174</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45862</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>45609</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45723</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45049</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45644</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45862</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45453</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45251</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45391</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46155</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>46009</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>45553</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45723</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44701</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44829</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46163</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>45063</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45454</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>45063</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45763</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45607</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45720</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>46085</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45698</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45723</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>46162</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>45441</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45726</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45975</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>46199</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46199</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45999</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45786</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45527</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>45786</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>46282</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>45517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>46282</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45792</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>46302</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>46303</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>46129</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45401</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>46140</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45579</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>45064</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45565</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45540</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45225</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45109</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>45225</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45433</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44623</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45226</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44826</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45517</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>44727</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>45723</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44585</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>45251</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>46029</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>46282</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44613</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44787</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>44691</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44496</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44641</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>44713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44706</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>44496</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44826</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44537</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44563</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44563</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44791</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44496</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44656</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>44509</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44734</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44608</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>44790</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44496</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44496</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>44804</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>44778</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44784</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44630</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44803</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>44714</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>44496</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44861</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44811</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44545</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44574</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44770</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44787</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44787</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>44531</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44581</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>44791</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45887</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45175</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44831</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>45469</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45219</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44741</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45891</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45891</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>45891</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>45891</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>45891</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>44824</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>45884</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45397</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45401</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45412</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45338</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45596</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45903</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44860</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45907</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>46162</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45034</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>46162</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45106</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>46163</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>46163</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>44809</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>46163</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45919</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>45922</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>46168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>46168</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>44883</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>46168</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45925</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>46171</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>46171</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45931</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>46174</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>46174</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>46174</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>46174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>44914</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45471</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>46176</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45936</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>45936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45936</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>45936</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45935</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>45429</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45625</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44886</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>46176</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45041</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45938</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>46174</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>46176</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>46176</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>45420</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>46176</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45945</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45945</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45420</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45378</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>46176</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45250</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45946</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45109</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>44496</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44859</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44995</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45947</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45947</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45947</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45131</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45947</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45947</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>45947</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45947</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45947</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>45950</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45950</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45950</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45952</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45952</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>46184</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>46184</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45953</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>46182</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44893</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>46184</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45919</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>46184</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45958</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45957</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45960</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45766</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45887</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45467</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45964</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45887</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45964</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45964</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45743</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45226</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45540</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45014</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45751</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45758</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45971</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>46178</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>45973</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>46199</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>46199</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>46199</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>46202</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44630</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45980</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>46202</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44683</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45980</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45980</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45153</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45454</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>46203</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>46202</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>46202</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45901</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45985</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>46206</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>45063</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>46206</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>46206</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>45793</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>46206</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45121</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45239</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>46191</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>46212</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45527</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45462</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45644</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45446</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45995</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>46153</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>45264</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>46223</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>46223</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>46223</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45777</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45777</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>46006</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45562</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45446</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>46008</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>46008</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>46008</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>46010</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46009</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>46010</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>46009</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>45572</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>45463</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45600</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45937</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45559</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>46240</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>46027</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45607</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>46239</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>46239</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>46239</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>46241</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>46283</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>46286</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>46286</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>46286</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>46286</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>46286</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>45019</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45600</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>46286</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>46038</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>46286</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45594</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>46283</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>46283</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45796</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>45527</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45664</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45797</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45503</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45578</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>45457</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>46045</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46288</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>46283</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>46288</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45800</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45125</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>46176</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>46051</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45804</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45968</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>46290</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>46057</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>46174</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45764</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>46072</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>46296</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45819</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45484</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45477</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>46251</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>44882</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45832</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>46084</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45833</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45833</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46297</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>46090</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>46090</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>46297</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45840</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>46094</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>45975</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>44895</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>46297</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>46098</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>45842</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>46098</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>46241</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45846</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>46098</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>46101</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>46101</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>46101</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>46255</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>46100</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>46100</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>46101</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>46101</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>46101</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>46104</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45846</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45846</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>45846</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>45012</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>46104</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32891,7 +32891,7 @@
         <v>45848</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>46051</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>45154</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45784</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33183,7 +33183,7 @@
         <v>45481</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>46113</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>45861</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>46113</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>46303</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>46303</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45522</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>45747</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>44776</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44792</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45420</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>46119</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>45867</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>46119</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44888</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>45575</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>46122</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>46122</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>46122</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>46122</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>46127</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>46127</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>46126</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>46129</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>46308</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45371</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>46210</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44909</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>46134</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45172</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>46308</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45208</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45644</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>46206</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45021</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>46268</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>46267</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>46136</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>46267</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>46267</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>46267</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>46268</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>46267</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>46267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>46267</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>45615</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>45986</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45757</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45490</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>46311</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>45428</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>46268</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>45579</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45818</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44914</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>44914</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>46316</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>46316</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>46316</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>46316</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>44916</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>46316</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>46316</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45163</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>46316</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>46316</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>45372</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>46275</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44666</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>45747</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>46141</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>46036</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45603</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>45558</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>46141</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>46127</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>46146</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45153</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>46150</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>46150</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>46150</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>46149</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>44718</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>46149</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>44950</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44496</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44834</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>46155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>45310</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>46157</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44515</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40164,7 +40164,7 @@
         <v>45319</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>46157</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45006</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>45319</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>45082</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>44897</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>45407</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45246</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45611</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45600</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>44776</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>44782</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>44803</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45140</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41201,7 +41201,7 @@
         <v>45188</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
         <v>44813</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>45188</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>45224</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45033</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>45478</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>44842</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>45193</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>45205</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>45173</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41956,7 +41956,7 @@
         <v>45735</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>45063</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>44659</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>45124</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>45014</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>44503</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44890</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45229</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>44896</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45751</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>44855</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45758</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45154</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45582</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45107</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45469</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45037</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>45429</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45477</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>45601</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>45106</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43534,7 +43534,7 @@
         <v>45424</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>44568</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45429</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>44987</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>45593</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45163</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>45377</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45106</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45625</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>45191</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>45501</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44377,7 +44377,7 @@
         <v>44748</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44450,7 +44450,7 @@
         <v>45589</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45670</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>44686</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45092</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>45751</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>44876</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>44734</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44976,7 +44976,7 @@
         <v>45428</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45700</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45122,7 +45122,7 @@
         <v>44845</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>44683</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>44683</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>44617</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45198</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45698</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>44700</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>45162</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45250</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45206</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45862,7 +45862,7 @@
         <v>45208</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45463</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>44726</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45408</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>44966</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>44966</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>44774</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>44790</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45018</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>44937</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>45077</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44895</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>44494</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>44508</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>45462</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45462</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45308</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>45470</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45545</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>44888</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>45572</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>44778</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44966</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>44966</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>44609</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>44686</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45607</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>44517</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>44517</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45540</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48102,7 +48102,7 @@
         <v>44517</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45867</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>45867</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45891</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>45945</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>45945</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48570,7 +48570,7 @@
         <v>45947</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45947</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45947</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48804,7 +48804,7 @@
         <v>45947</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45947</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>45985</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49038,7 +49038,7 @@
         <v>46162</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>46199</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
